--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44882</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45996</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45980</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45996</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46142</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44861</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45996</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45524</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45160</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44628</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45996</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>46001</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45236</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44867</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>45973</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45180</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45555</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45968</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>45236</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45569</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45973</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45180</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44908</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45147</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>46272</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>45846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44748</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44595</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44617</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44746</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44494</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44825</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44484</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44813</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44459</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44621</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>44805</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>44484</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>44804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44530</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44579</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44662</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44571</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44503</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44795</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45175</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45338</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>45597</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44792</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45160</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45439</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45349</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>45391</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45092</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45344</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45771</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45771</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>45377</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45160</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>44917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44988</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45337</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45225</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45408</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>44998</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45400</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44813</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44813</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45744</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45090</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45089</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45021</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44872</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44874</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45260</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>45532</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44872</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44467</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45233</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45561</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45819</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45896</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45338</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45701</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45554</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45786</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45905</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45536</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45132</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45915</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45126</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45126</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45920</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45261</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44522</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45271</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>46142</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45338</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44522</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44522</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45709</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44886</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45260</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45377</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45950</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44708</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45771</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45216</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45771</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>46153</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44993</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44993</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>46155</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45392</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45968</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45968</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45975</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45048</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44483</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45403</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45986</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45441</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45441</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>46161</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>46161</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>46161</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>46161</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44879</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45992</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>46161</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>46161</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45572</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45161</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45536</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45996</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45344</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45600</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44907</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45537</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44963</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45740</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>46029</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>46035</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>46034</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>46035</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>46036</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>46036</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46036</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45558</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>46171</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46045</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45127</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46048</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46048</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45209</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>46051</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>46051</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45132</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45132</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44790</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44795</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44475</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44475</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45240</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46178</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44988</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46178</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>46178</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44732</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>46029</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45525</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45240</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45240</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>46178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>46069</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>46069</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>46069</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>46069</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>46073</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>46073</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45454</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>46084</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>46185</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>46085</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44484</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45747</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>46185</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>46185</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>46185</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45448</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45261</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>46104</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46104</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46198</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>46105</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>46106</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45234</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46105</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45245</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46198</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45537</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45537</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46198</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45240</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46112</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45344</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45230</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46202</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45734</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44949</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45525</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45259</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>46202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>46202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46244</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45377</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45366</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45622</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45358</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45819</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>44528</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45734</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44494</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44602</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44746</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45240</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45240</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44503</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45503</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45503</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45159</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>46212</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>44987</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45134</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45134</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45306</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45089</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45089</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45741</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44503</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45771</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45771</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45782</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45062</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45338</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46279</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45791</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46237</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45625</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45821</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45821</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45821</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45827</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45827</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45840</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45873</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45873</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45880</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45701</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>45734</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45362</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45016</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44889</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45007</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45362</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45117</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44903</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45195</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45740</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45744</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45744</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45767</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45771</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45782</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45821</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45968</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>46262</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44882</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45996</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45996</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44861</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45996</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>46142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45261</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44867</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45996</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>46001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>45463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45555</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>44988</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44748</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45180</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>46272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44813</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45147</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45569</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44908</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44484</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44662</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44805</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44484</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44530</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44579</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44662</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44571</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44503</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>44988</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45230</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44813</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45377</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45377</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44795</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45441</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45226</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45454</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44790</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44483</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45306</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>46029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44475</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>46034</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45701</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>46035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>46035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>46036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45896</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46048</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46045</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46048</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>46051</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46029</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45537</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45915</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45391</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44998</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45920</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>46069</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>46069</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>46069</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>46069</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>46073</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>46073</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45338</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>46084</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45377</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44708</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>46104</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46105</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45950</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>46106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45958</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>46112</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45175</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45089</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45968</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45968</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45967</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44988</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45975</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45625</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44522</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45986</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45240</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45554</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45996</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44528</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45408</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45132</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45132</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44522</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45240</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45786</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46003</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45021</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45532</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44879</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45821</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>45821</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45821</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45734</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45622</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45132</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>46142</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45240</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45827</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45827</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45771</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45771</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45245</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>44503</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45260</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44475</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44484</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45090</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>44886</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45400</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>46029</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>46155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45698</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45740</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>46155</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45338</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45536</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45600</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46161</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>46161</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46161</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45840</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>46161</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>46161</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>46161</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>46161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45160</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45344</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45261</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45358</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45337</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>46171</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45134</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>46178</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>46178</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>46178</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>46178</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>46185</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45873</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46185</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46185</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>46185</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>46185</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44993</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44503</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44522</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45261</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45873</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45349</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>46198</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>46198</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45561</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45734</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45701</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>46202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46202</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>46202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45597</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44732</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45771</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45771</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46212</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45159</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44792</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>45741</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45234</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45744</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44797</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45771</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45338</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45260</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45448</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>44874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44792</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45344</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44795</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44872</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45537</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45537</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>46237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45403</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>46279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45344</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45536</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44503</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>44602</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44907</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44949</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45572</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>44917</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45558</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45271</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45225</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>44963</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45525</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45392</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44746</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45439</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45126</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45126</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45089</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45240</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45240</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45233</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45709</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45134</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45503</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45441</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45525</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45593</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45366</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45734</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45259</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45384</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45338</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45175</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45216</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45062</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45338</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45791</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45016</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44889</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45007</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45117</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>44903</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45007</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45740</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45744</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45744</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45767</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45771</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45782</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45821</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45968</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46262</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44882</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45996</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45996</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44861</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45996</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>46142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45261</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44867</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44867</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45996</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>46001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45236</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>45463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45555</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>44988</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44748</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45180</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>46272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44813</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45147</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45569</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44908</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44484</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44662</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44805</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44484</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44530</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44579</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44662</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44571</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44503</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>44988</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45230</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44813</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45377</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45377</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44795</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45441</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45226</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45454</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44790</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44483</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45306</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>46029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44475</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>46034</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45701</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>46035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>46035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>46036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45896</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46048</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46045</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46048</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>46051</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46029</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45537</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45915</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45391</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44998</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45920</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>46069</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>46069</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>46069</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>46069</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>46073</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>46073</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45338</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>46084</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45377</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44708</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>46104</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46105</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45950</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>46106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45601</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45958</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>46112</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45175</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45089</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45968</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45968</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45967</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44988</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45975</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45625</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44522</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45986</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45240</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45554</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45996</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44528</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45408</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45132</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45132</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44522</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45240</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45786</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46003</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45021</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45532</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44879</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45821</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>45821</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45821</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45747</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45734</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45622</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45132</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>46142</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45240</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45827</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45827</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45771</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45771</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45245</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>44503</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45260</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44475</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>44484</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45090</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>44886</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45400</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>46029</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>46155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45698</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45740</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>46155</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45338</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45536</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45600</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46161</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>46161</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46161</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45840</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>46161</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>46161</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>46161</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>46161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45160</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45344</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45261</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45358</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45337</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>46171</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45134</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>46178</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>46178</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>46178</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>46178</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>46185</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45873</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46185</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46185</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>46185</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>46185</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44993</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44503</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44522</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45261</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45873</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45349</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>46198</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>46198</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45561</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45734</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45701</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>46202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46202</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>46202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45597</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44732</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45771</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45771</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46212</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45159</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44792</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>45741</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45234</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45744</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44797</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45771</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45338</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45260</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45448</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>44874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44792</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45344</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44795</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44872</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45537</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45537</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>46237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45403</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>46279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45344</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45536</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44503</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>44602</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44907</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44949</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45572</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>44917</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45558</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45271</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45225</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>44963</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45525</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45392</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44746</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45439</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45126</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45126</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45089</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45240</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45240</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45233</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45709</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45134</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45503</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45441</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45525</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45593</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45366</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45734</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45259</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45384</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45338</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45175</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45216</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45062</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45338</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45791</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45016</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44889</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45007</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45117</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>44903</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45007</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45740</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45744</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45744</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45767</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45771</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45782</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45821</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45968</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46262</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>44882</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45996</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>45254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45996</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46008</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45996</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>46142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>46273</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45524</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46001</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45236</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45996</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44628</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45236</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45180</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44748</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>45555</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45569</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>44813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>46272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44988</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>44908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45147</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44484</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44662</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44805</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44484</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44530</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44579</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44662</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44571</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>44503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44503</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45338</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45597</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44792</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45175</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45160</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45439</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45349</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45384</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45092</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>45344</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45377</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45391</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44475</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45701</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45771</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45771</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>46003</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45819</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45896</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45160</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46035</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>46034</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>46035</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>46036</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>46036</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>46036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46045</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>46048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>46048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>46051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45920</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45225</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>46029</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45408</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46069</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44998</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>46069</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>46069</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45400</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46073</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>46073</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44813</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45950</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>46084</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>45744</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45090</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45968</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>46104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45089</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45975</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46104</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>46105</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>46105</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>46105</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45980</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45821</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45821</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45821</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45021</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>46112</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44792</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44872</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45992</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45827</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44874</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45996</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45260</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44872</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45233</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45622</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45561</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45338</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44528</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45840</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45600</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45532</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45536</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45126</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45126</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45261</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45271</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45554</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45786</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45338</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44522</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45132</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44522</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45709</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44886</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45873</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44522</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>46142</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45377</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45873</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44708</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45771</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45216</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45771</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44993</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>44993</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46155</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>46155</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45698</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>46029</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45392</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46161</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46161</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>46161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45175</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45338</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>46161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44483</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45880</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45403</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45441</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45441</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45701</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44879</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45734</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>46171</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>46178</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46178</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>46178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>46178</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45572</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45536</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46185</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>46185</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46185</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45261</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45344</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45600</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44907</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>46198</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46198</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45537</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>46198</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>46202</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>44963</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46202</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45740</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45558</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46212</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45127</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45132</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45132</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44790</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44795</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44475</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44475</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45240</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44988</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44732</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45525</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45240</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45240</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45454</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44484</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45747</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45448</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45234</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45537</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45537</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45344</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45230</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45734</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44949</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45525</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45259</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45377</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45366</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45358</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45734</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44494</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44602</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>44746</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45240</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45240</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44503</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45503</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45159</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44987</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45134</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45134</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45306</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45089</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45089</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45741</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44503</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45771</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45771</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45062</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45338</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>45362</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45016</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44889</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45007</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45362</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45117</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44903</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45007</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45195</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45740</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45744</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45744</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45767</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45771</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45782</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45821</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45968</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>46262</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="U2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>44882</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45996</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>45254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45996</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46008</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45996</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>46142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>46273</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45524</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46001</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45236</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45996</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44628</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45463</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45236</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45180</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44748</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>45555</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45569</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>44813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>46272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44988</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>44908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45147</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44484</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44662</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44805</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44484</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44530</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44579</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44662</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44571</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>44503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44503</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45338</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45597</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>44792</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45175</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45160</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45439</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45349</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45384</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45092</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>45344</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45377</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45391</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44475</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45701</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45771</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45771</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>46003</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45819</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45896</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>44917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45160</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46035</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>46034</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>46035</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>46036</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>46036</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>46036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46045</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>46048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>46048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>46051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45920</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45225</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>46029</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45408</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46069</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44998</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>46069</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>46069</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45400</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46073</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>46073</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44813</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45950</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>46084</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>45744</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45090</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45968</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45968</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>46104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45089</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45975</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46104</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>46105</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>46105</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>46105</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45980</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45821</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45821</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45821</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45021</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>46112</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44792</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44872</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45992</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45827</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44874</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45996</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45260</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44872</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45233</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45622</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45561</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45338</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44528</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45840</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45600</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45532</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45536</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45126</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45126</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45261</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45271</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45554</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45786</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45338</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44522</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45132</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44522</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45709</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44886</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45873</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44522</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>46142</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45377</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45873</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44708</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45771</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45216</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45771</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44993</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>44993</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46155</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>46155</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45698</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>46029</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45392</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46161</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46161</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>46161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>46161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45175</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45338</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>46161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44483</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45880</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45403</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45441</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45441</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45701</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44879</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45734</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>46171</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>46178</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46178</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>46178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>46178</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45572</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45536</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46185</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>46185</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46185</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45261</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45344</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45600</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44907</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>46198</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46198</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45537</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>46198</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>46202</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>44963</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46202</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45740</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45558</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46212</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45127</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45132</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45132</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44790</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44795</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44475</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44475</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45240</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44988</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44732</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45525</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45240</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45240</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45454</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46279</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44484</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45747</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45448</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45234</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45537</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45537</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45344</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45230</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45734</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44949</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45525</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45259</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45377</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45366</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45358</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45734</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44494</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44602</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>44746</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45240</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45240</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44503</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45503</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45159</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44987</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45134</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45134</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45306</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45089</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45089</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45741</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44503</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45771</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45771</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45062</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45338</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>45362</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45016</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44889</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45007</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45362</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45117</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44903</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45007</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45195</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45740</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45744</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45744</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45767</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45771</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45782</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45821</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45968</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>46262</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>44882</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45996</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45996</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44861</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45996</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>46142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45261</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45160</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45463</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45996</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46001</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45236</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45180</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45569</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45968</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44748</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45180</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44988</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45973</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45236</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45555</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>46272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44617</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>44803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44484</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44662</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44805</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44530</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44579</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44503</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44621</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44484</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44897</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45160</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45240</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45240</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45441</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45226</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45709</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45400</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45740</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44988</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45338</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45134</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45377</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45377</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44813</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>44813</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45454</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45503</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45503</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44790</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45160</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45048</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45441</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44795</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45344</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>45261</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45525</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45358</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44483</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45306</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45593</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45819</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45366</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45734</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45259</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45384</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45819</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45896</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45338</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45092</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45134</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>45216</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45161</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45782</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45062</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44993</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44993</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44522</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45338</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45920</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45391</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44998</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45349</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45791</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45338</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45600</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45377</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44708</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45597</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45601</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44732</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45625</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45175</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45771</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45821</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>45821</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45821</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45089</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45950</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45827</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45827</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45958</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44988</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45159</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45968</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45967</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45741</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45234</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45744</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44797</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45408</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45771</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45132</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45132</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45975</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45338</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45240</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45240</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45260</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45021</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45448</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45873</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44874</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45873</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>44792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45880</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45127</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>44795</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45701</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>44872</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45537</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45734</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45537</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45403</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45344</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>46104</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>46105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>46104</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>46105</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45240</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>46105</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45771</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45771</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>46106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44503</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>46112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45992</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44503</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44602</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44907</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45996</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44949</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45572</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>44494</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>46003</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45558</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45271</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44528</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44522</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45225</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>46029</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45786</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44963</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45525</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45392</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>46036</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>46035</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45532</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>46035</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46036</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>44746</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45819</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45439</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45126</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45126</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>46048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>46045</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>46048</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>45622</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45132</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46142</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45089</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>46029</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46069</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46069</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>46069</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>46069</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>46073</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46073</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>46084</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>46029</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46155</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45698</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>46161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>46161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46161</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>46161</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46161</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46161</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46161</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46171</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>46178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>46178</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>46178</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46185</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46185</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45261</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46198</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>46212</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46237</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>46300</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45362</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45016</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>44889</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45007</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45362</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45117</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>44903</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45007</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45195</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45740</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45744</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45744</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45767</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45771</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45782</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45821</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46262</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>44882</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45996</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45996</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44861</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45996</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>46142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45261</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45160</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45463</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45996</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46001</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45236</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45180</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45147</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45569</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45968</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44748</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45180</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44988</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45973</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45236</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45555</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>46272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44617</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>44803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44484</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44662</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44805</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44530</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44579</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44503</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44621</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44484</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>45090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44897</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45160</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45240</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45240</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45441</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45226</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45709</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45400</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45740</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44988</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45338</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45134</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45377</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45377</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44813</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>44813</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45454</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45503</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45503</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44790</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45160</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45048</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45441</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44795</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45344</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>45261</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45525</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45358</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44483</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45306</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45593</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45819</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45366</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45734</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45259</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45384</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45819</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45896</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45338</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45092</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45175</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45134</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>45216</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45161</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45782</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45062</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44993</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44993</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44522</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45338</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45920</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45391</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44998</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45349</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45791</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45338</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45600</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45377</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44708</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45597</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45601</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44732</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45625</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45175</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45771</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45821</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>45821</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45821</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45089</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45950</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45827</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45827</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45958</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44988</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45159</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45968</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45967</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45741</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45234</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45744</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44797</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45408</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45771</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45132</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45132</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45975</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45338</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45240</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45240</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45260</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45021</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45448</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45873</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44874</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45873</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>44792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45880</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45127</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>44795</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45701</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>44872</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45537</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45734</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45537</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45403</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45344</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>46104</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>46105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>46104</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>46105</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45240</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>46105</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45771</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45771</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>46106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44503</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>46112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45992</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44503</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44602</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44907</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45996</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>44949</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45572</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>44494</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>46003</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45558</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45271</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44528</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44522</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45225</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>46029</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45786</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>44963</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45525</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45392</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>46036</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>46035</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45532</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>46035</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46036</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>44746</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45819</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45439</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45126</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45126</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>46048</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>46045</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>46048</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>45622</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45132</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46142</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45089</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>46029</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46069</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46069</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>46069</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>46069</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>46073</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46073</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>46084</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>46029</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46155</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45698</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>46161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>46161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46161</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>46161</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46161</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46161</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46161</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46171</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>46178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>46178</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>46178</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46185</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46185</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45261</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46198</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>46212</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46237</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>46300</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45362</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45016</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>44889</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45007</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45362</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45117</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>44903</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45007</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45195</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45740</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45744</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45744</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45767</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45771</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45782</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45821</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46262</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -622,13 +622,13 @@
         <v>1887.5</v>
       </c>
       <c r="J2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" t="n">
         <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -643,19 +643,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R2" t="n">
         <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T2" t="n">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="U2" t="n">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -673,6 +673,7 @@
 Fjällig taggsvamp s.str.
 Gullklöver
 Jungfrulin
+Järnsparv
 Kattfotslav
 Kricka
 Kungsörn
@@ -783,7 +784,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +917,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1049,7 @@
         <v>44882</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1173,7 +1174,7 @@
         <v>46268</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1298,7 +1299,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1424,7 @@
         <v>45254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1540,7 @@
         <v>45996</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1661,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1780,7 +1781,7 @@
         <v>45996</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1900,7 +1901,7 @@
         <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2015,7 +2016,7 @@
         <v>45980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2134,7 +2135,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2253,7 +2254,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2366,7 +2367,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2484,7 +2485,7 @@
         <v>46142</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2601,7 +2602,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2719,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2836,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2943,7 +2944,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3060,7 +3061,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3172,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3287,7 +3288,7 @@
         <v>45524</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3398,7 +3399,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3514,7 +3515,7 @@
         <v>44889</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3630,7 +3631,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3741,7 +3742,7 @@
         <v>44803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3852,7 +3853,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3958,7 +3959,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4068,7 +4069,7 @@
         <v>45996</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4179,7 +4180,7 @@
         <v>46001</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4294,7 +4295,7 @@
         <v>45236</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4409,7 +4410,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4524,7 +4525,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4640,7 @@
         <v>45973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4755,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4865,7 +4866,7 @@
         <v>45463</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4981,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5086,7 @@
         <v>45180</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5195,7 +5196,7 @@
         <v>45555</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5305,7 +5306,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5415,7 +5416,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5520,7 +5521,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5635,7 @@
         <v>45569</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5749,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5862,7 +5863,7 @@
         <v>45973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5976,7 +5977,7 @@
         <v>44988</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6086,7 +6087,7 @@
         <v>46272</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6196,7 +6197,7 @@
         <v>45180</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6306,7 +6307,7 @@
         <v>44908</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6411,7 +6412,7 @@
         <v>45147</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6517,7 @@
         <v>45259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6621,7 +6622,7 @@
         <v>45846</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6731,7 +6732,7 @@
         <v>44748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6846,7 @@
         <v>44595</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6918,7 +6919,7 @@
         <v>44803</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6996,7 +6997,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7074,7 +7075,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7152,7 +7153,7 @@
         <v>44617</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7226,7 @@
         <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7298,7 +7299,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7376,7 +7377,7 @@
         <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7449,7 +7450,7 @@
         <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7527,7 +7528,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7605,7 +7606,7 @@
         <v>44621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7678,7 +7679,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7756,7 +7757,7 @@
         <v>44803</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7834,7 +7835,7 @@
         <v>44805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7907,7 +7908,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7980,7 +7981,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8058,7 +8059,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8136,7 +8137,7 @@
         <v>44579</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8209,7 +8210,7 @@
         <v>44662</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8287,7 +8288,7 @@
         <v>44571</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8365,7 +8366,7 @@
         <v>44503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8443,7 +8444,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8521,7 +8522,7 @@
         <v>44795</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8594,7 +8595,7 @@
         <v>45338</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8667,7 +8668,7 @@
         <v>45175</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8740,7 +8741,7 @@
         <v>45597</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8818,7 +8819,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8891,7 +8892,7 @@
         <v>45160</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8964,7 +8965,7 @@
         <v>45439</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9037,7 +9038,7 @@
         <v>45349</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9110,7 +9111,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9188,7 +9189,7 @@
         <v>45384</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9266,7 +9267,7 @@
         <v>45092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9344,7 +9345,7 @@
         <v>45377</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9422,7 +9423,7 @@
         <v>45344</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9495,7 +9496,7 @@
         <v>45771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9573,7 +9574,7 @@
         <v>45771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9651,7 +9652,7 @@
         <v>45391</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9724,7 +9725,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9797,7 +9798,7 @@
         <v>45160</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9870,7 +9871,7 @@
         <v>44797</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9943,7 +9944,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10021,7 +10022,7 @@
         <v>45337</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10099,7 +10100,7 @@
         <v>45225</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10172,7 +10173,7 @@
         <v>44897</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10250,7 +10251,7 @@
         <v>44998</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10323,7 +10324,7 @@
         <v>45400</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10401,7 +10402,7 @@
         <v>45408</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10479,7 +10480,7 @@
         <v>44813</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10557,7 +10558,7 @@
         <v>44813</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10635,7 +10636,7 @@
         <v>45744</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10713,7 +10714,7 @@
         <v>44503</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10791,7 +10792,7 @@
         <v>45090</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10869,7 +10870,7 @@
         <v>45601</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10942,7 +10943,7 @@
         <v>45089</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11020,7 +11021,7 @@
         <v>45021</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11093,7 +11094,7 @@
         <v>45532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11166,7 +11167,7 @@
         <v>44792</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11239,7 +11240,7 @@
         <v>44872</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11317,7 +11318,7 @@
         <v>44874</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11395,7 +11396,7 @@
         <v>45260</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11473,7 +11474,7 @@
         <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11546,7 +11547,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11624,7 +11625,7 @@
         <v>45896</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11697,7 +11698,7 @@
         <v>45233</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11775,7 +11776,7 @@
         <v>45701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11853,7 +11854,7 @@
         <v>45819</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11926,7 +11927,7 @@
         <v>45554</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12004,7 +12005,7 @@
         <v>45786</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12082,7 +12083,7 @@
         <v>45132</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12155,7 +12156,7 @@
         <v>45561</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12228,7 +12229,7 @@
         <v>44522</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12301,7 +12302,7 @@
         <v>45593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12379,7 +12380,7 @@
         <v>46142</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12457,7 +12458,7 @@
         <v>45338</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12530,7 +12531,7 @@
         <v>45915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12603,7 +12604,7 @@
         <v>45600</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12676,7 +12677,7 @@
         <v>45920</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12749,7 +12750,7 @@
         <v>45536</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12822,7 +12823,7 @@
         <v>45126</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12895,7 +12896,7 @@
         <v>45126</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12968,7 +12969,7 @@
         <v>45261</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13046,7 +13047,7 @@
         <v>45271</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13119,7 +13120,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13192,7 +13193,7 @@
         <v>44522</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13265,7 +13266,7 @@
         <v>46155</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13343,7 +13344,7 @@
         <v>45950</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13421,7 +13422,7 @@
         <v>46155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13499,7 +13500,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13577,7 +13578,7 @@
         <v>46029</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13655,7 +13656,7 @@
         <v>45958</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13728,7 +13729,7 @@
         <v>44522</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13801,7 +13802,7 @@
         <v>45709</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13879,7 +13880,7 @@
         <v>46161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13957,7 +13958,7 @@
         <v>46161</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14035,7 +14036,7 @@
         <v>46161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14113,7 +14114,7 @@
         <v>44886</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14186,7 +14187,7 @@
         <v>46161</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14264,7 +14265,7 @@
         <v>46161</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14342,7 +14343,7 @@
         <v>46161</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14420,7 +14421,7 @@
         <v>45260</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14498,7 +14499,7 @@
         <v>45967</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14571,7 +14572,7 @@
         <v>46161</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14649,7 +14650,7 @@
         <v>45377</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14727,7 +14728,7 @@
         <v>45968</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14805,7 +14806,7 @@
         <v>44708</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14878,7 +14879,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14956,7 +14957,7 @@
         <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15029,7 +15030,7 @@
         <v>45216</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15102,7 +15103,7 @@
         <v>45771</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15180,7 +15181,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15253,7 +15254,7 @@
         <v>44993</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15331,7 +15332,7 @@
         <v>44993</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15409,7 +15410,7 @@
         <v>45986</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15487,7 +15488,7 @@
         <v>45392</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15565,7 +15566,7 @@
         <v>45175</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15638,7 +15639,7 @@
         <v>45992</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15716,7 +15717,7 @@
         <v>45338</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15789,7 +15790,7 @@
         <v>45048</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15867,7 +15868,7 @@
         <v>45996</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15945,7 +15946,7 @@
         <v>45403</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16018,7 +16019,7 @@
         <v>46003</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16091,7 +16092,7 @@
         <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16164,7 +16165,7 @@
         <v>45441</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16237,7 +16238,7 @@
         <v>44879</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16310,7 +16311,7 @@
         <v>46171</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16388,7 +16389,7 @@
         <v>45572</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16461,7 +16462,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16534,7 +16535,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16612,7 +16613,7 @@
         <v>45536</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16685,7 +16686,7 @@
         <v>46035</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16763,7 +16764,7 @@
         <v>46034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16841,7 +16842,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16919,7 +16920,7 @@
         <v>46036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16997,7 +16998,7 @@
         <v>46036</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17075,7 +17076,7 @@
         <v>46036</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17153,7 +17154,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17231,7 +17232,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17309,7 +17310,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17387,7 +17388,7 @@
         <v>46178</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17465,7 +17466,7 @@
         <v>46045</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17538,7 +17539,7 @@
         <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17611,7 +17612,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17684,7 +17685,7 @@
         <v>46051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17762,7 +17763,7 @@
         <v>45344</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17835,7 +17836,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17908,7 +17909,7 @@
         <v>44907</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17986,7 +17987,7 @@
         <v>46029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18064,7 +18065,7 @@
         <v>45537</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18142,7 +18143,7 @@
         <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18220,7 +18221,7 @@
         <v>46069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18298,7 +18299,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18376,7 +18377,7 @@
         <v>46069</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18454,7 +18455,7 @@
         <v>46069</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18532,7 +18533,7 @@
         <v>44963</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18605,7 +18606,7 @@
         <v>45740</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18683,7 +18684,7 @@
         <v>46073</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18761,7 +18762,7 @@
         <v>46073</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18839,7 +18840,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18917,7 +18918,7 @@
         <v>46185</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18995,7 +18996,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19073,7 +19074,7 @@
         <v>46185</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19151,7 +19152,7 @@
         <v>46084</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19229,7 +19230,7 @@
         <v>45261</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19307,7 +19308,7 @@
         <v>45558</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19385,7 +19386,7 @@
         <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19458,7 +19459,7 @@
         <v>46104</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19536,7 +19537,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19609,7 +19610,7 @@
         <v>45132</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19682,7 +19683,7 @@
         <v>45132</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19755,7 +19756,7 @@
         <v>44790</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19833,7 +19834,7 @@
         <v>44795</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19906,7 +19907,7 @@
         <v>46104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19984,7 +19985,7 @@
         <v>45240</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20057,7 +20058,7 @@
         <v>44988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20135,7 +20136,7 @@
         <v>46105</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20213,7 +20214,7 @@
         <v>46105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20291,7 +20292,7 @@
         <v>46106</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20369,7 +20370,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20447,7 +20448,7 @@
         <v>46198</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20520,7 +20521,7 @@
         <v>44732</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20593,7 +20594,7 @@
         <v>46112</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20671,7 +20672,7 @@
         <v>46198</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20744,7 +20745,7 @@
         <v>45525</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20817,7 +20818,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20890,7 +20891,7 @@
         <v>45240</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20963,7 +20964,7 @@
         <v>46202</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21041,7 +21042,7 @@
         <v>46202</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21119,7 +21120,7 @@
         <v>46202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21197,7 +21198,7 @@
         <v>45454</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21270,7 +21271,7 @@
         <v>45622</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21348,7 +21349,7 @@
         <v>45819</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21421,7 +21422,7 @@
         <v>45747</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21494,7 +21495,7 @@
         <v>44528</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21572,7 +21573,7 @@
         <v>45448</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21645,7 +21646,7 @@
         <v>46212</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21723,7 +21724,7 @@
         <v>45234</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21796,7 +21797,7 @@
         <v>45245</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21869,7 +21870,7 @@
         <v>45537</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21947,7 +21948,7 @@
         <v>45537</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22025,7 +22026,7 @@
         <v>45240</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22098,7 +22099,7 @@
         <v>45344</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22171,7 +22172,7 @@
         <v>45734</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22244,7 +22245,7 @@
         <v>44949</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22317,7 +22318,7 @@
         <v>45525</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22390,7 +22391,7 @@
         <v>45259</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22468,7 +22469,7 @@
         <v>45377</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22546,7 +22547,7 @@
         <v>45366</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22624,7 +22625,7 @@
         <v>45358</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22697,7 +22698,7 @@
         <v>46279</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22770,7 +22771,7 @@
         <v>45734</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22843,7 +22844,7 @@
         <v>46237</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22916,7 +22917,7 @@
         <v>44494</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22989,7 +22990,7 @@
         <v>44602</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23062,7 +23063,7 @@
         <v>44746</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23140,7 +23141,7 @@
         <v>45240</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23213,7 +23214,7 @@
         <v>45240</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23286,7 +23287,7 @@
         <v>44503</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23364,7 +23365,7 @@
         <v>45503</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23437,7 +23438,7 @@
         <v>45503</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23510,7 +23511,7 @@
         <v>45159</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23588,7 +23589,7 @@
         <v>44987</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23661,7 +23662,7 @@
         <v>45134</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23734,7 +23735,7 @@
         <v>45134</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23807,7 +23808,7 @@
         <v>45306</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23880,7 +23881,7 @@
         <v>45089</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23958,7 +23959,7 @@
         <v>45089</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24036,7 +24037,7 @@
         <v>45741</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24114,7 +24115,7 @@
         <v>44503</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24192,7 +24193,7 @@
         <v>45771</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24270,7 +24271,7 @@
         <v>45771</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24348,7 +24349,7 @@
         <v>46300</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24421,7 +24422,7 @@
         <v>45782</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24499,7 +24500,7 @@
         <v>45062</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24572,7 +24573,7 @@
         <v>45338</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24645,7 +24646,7 @@
         <v>45791</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24723,7 +24724,7 @@
         <v>45042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24796,7 +24797,7 @@
         <v>45625</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24869,7 +24870,7 @@
         <v>45821</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24947,7 +24948,7 @@
         <v>45821</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25025,7 +25026,7 @@
         <v>45821</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25103,7 +25104,7 @@
         <v>45827</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25181,7 +25182,7 @@
         <v>45827</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25259,7 +25260,7 @@
         <v>45840</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25337,7 +25338,7 @@
         <v>45873</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25415,7 +25416,7 @@
         <v>45873</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25493,7 +25494,7 @@
         <v>45880</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25566,7 +25567,7 @@
         <v>45701</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25644,7 +25645,7 @@
         <v>45734</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25722,7 +25723,7 @@
         <v>45362</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25800,7 +25801,7 @@
         <v>45016</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25878,7 +25879,7 @@
         <v>44889</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25956,7 +25957,7 @@
         <v>45007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26034,7 +26035,7 @@
         <v>45362</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26112,7 +26113,7 @@
         <v>45117</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26190,7 +26191,7 @@
         <v>44903</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26268,7 +26269,7 @@
         <v>45007</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26346,7 +26347,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26424,7 +26425,7 @@
         <v>45740</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26502,7 +26503,7 @@
         <v>45744</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26580,7 +26581,7 @@
         <v>45744</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26658,7 +26659,7 @@
         <v>45767</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26731,7 +26732,7 @@
         <v>45771</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26809,7 +26810,7 @@
         <v>45782</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26887,7 +26888,7 @@
         <v>45821</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26965,7 +26966,7 @@
         <v>45968</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27043,7 +27044,7 @@
         <v>46262</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>70</v>
       </c>
       <c r="T2" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="U2" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44882</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>46268</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>45254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>45996</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45996</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46142</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>45524</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44889</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45996</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46001</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45236</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>44867</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45463</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45180</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45555</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45569</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44988</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>46272</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>45180</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44908</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>45147</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45846</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44595</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44803</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44617</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44803</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44579</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44662</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44571</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44795</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45338</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>45175</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45597</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45160</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45439</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45349</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45384</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45377</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45344</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>45771</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45391</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45160</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44797</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45337</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45225</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44897</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44998</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45400</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45408</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44813</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44813</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45744</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44503</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45090</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45601</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45089</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45021</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>44792</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44872</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44874</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45260</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45896</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45233</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45819</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45554</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45786</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45132</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45561</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44522</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46142</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45338</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45600</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45920</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45536</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45126</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45126</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45261</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45271</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44522</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46155</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45950</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>46155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>46029</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45958</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44522</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45709</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>46161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>46161</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>46161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44886</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>46161</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>46161</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>46161</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45260</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45967</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46161</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45377</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45968</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44708</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45216</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45771</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>44993</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44993</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45986</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45392</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45175</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45992</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45338</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45048</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45996</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45403</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>46003</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45441</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44879</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>46171</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45572</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45536</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>46035</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>46034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>46036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>46036</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>46036</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46178</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46045</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45344</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44907</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45537</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>46069</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46069</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>44963</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>45740</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46073</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46073</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>46185</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>46185</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>46084</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45261</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45558</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46104</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45132</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45132</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44790</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44795</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>46104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45240</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>46105</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>46105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>46106</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46198</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44732</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>46112</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>46198</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45525</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45240</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>46202</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>46202</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>46202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45454</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45622</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45819</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45747</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44528</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45448</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>46212</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45234</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45245</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45537</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45537</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45240</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45344</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45734</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44949</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45525</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45259</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45377</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45366</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45358</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>46279</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45734</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>46237</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44494</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>44602</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44746</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45240</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45240</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44503</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45503</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45503</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45159</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44987</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45134</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45134</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>45306</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45089</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45089</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45741</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>44503</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45771</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45771</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46300</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45782</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45062</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45338</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45791</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45625</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45821</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45821</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45821</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45827</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45827</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45840</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45873</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45873</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45880</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45701</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45734</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45362</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45016</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>44889</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45362</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45117</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44903</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45007</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45740</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45744</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45744</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45767</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45771</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45782</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45821</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45968</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46262</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>70</v>
       </c>
       <c r="T2" t="n">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="U2" t="n">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>46268</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>44882</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>45996</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44861</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>45524</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45261</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44889</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44628</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45996</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>46001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45236</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>45160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>44813</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45569</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45236</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45973</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44748</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45555</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>46272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45180</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45180</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44595</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44803</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44617</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44494</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44803</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44579</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44662</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44503</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44571</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>45819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44988</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>45819</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45377</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45377</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44813</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44917</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45558</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45896</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45048</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>44795</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45271</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>46161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>46161</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>45225</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44963</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>46161</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>46161</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>46161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>45525</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45392</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45920</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>44746</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>46171</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>45439</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45126</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45126</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45089</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45160</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45441</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45240</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45240</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45226</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45233</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45454</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>46178</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44790</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45950</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>46178</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45709</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>46178</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>46178</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45134</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>45958</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>46185</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>46185</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>46185</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>46185</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>46185</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45261</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45503</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45503</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45441</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45968</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45525</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>46198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>46198</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45593</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45975</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>45980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>46202</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>46202</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>46202</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45366</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45734</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45259</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45384</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45986</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45338</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45092</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45992</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45175</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45306</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46212</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45996</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45216</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45782</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>46003</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45062</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46237</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>46279</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45338</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>46029</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>46036</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>46035</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>46036</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>46036</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>46048</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>46045</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46048</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>46051</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>46029</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45625</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>46069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>46069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>46069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45821</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45821</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45821</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46073</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46073</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45827</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46084</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45840</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46104</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>46105</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>46104</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>46105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>46105</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46106</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>46300</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>46112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45873</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45873</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45880</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45701</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44872</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45554</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45537</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44528</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44522</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45391</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45786</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>44998</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45532</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45819</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45338</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45132</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>46142</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45377</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>44708</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>46029</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>46155</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45698</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45601</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>46155</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45175</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45089</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45089</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>44988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>44522</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45240</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45408</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45132</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45132</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45240</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45021</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44987</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44879</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45127</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45747</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45734</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45240</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45771</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44503</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45260</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45090</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44897</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44886</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45400</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45740</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45338</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45536</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45600</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45160</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45344</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45261</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45358</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45337</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45134</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45161</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>44503</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44522</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45349</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45561</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45600</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45597</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>44732</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45771</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45771</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45771</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45159</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>44792</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45234</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45744</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>44797</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45771</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45338</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45260</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45448</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44874</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44792</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45344</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44795</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44872</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45537</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45537</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45403</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45344</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45536</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>44602</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44907</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44949</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>44494</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45362</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45016</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>44889</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45362</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45117</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44903</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45007</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45740</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45744</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45744</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45767</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45771</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45782</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45821</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45968</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46262</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt LAXÅ.xlsx
+++ b/Översikt LAXÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44662</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>70</v>
       </c>
       <c r="T2" t="n">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="U2" t="n">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>45559</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>44867</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>46268</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>44882</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>45996</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44867</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45980</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45973</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44861</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45996</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44889</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>45524</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45261</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44889</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44628</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45996</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>46001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45236</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44867</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44867</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>45160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45463</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>44813</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45147</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45569</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45236</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45973</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44748</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45555</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>46272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45180</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45180</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6829,24 +6829,24 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5441-2022</t>
+          <t>S 1135-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44595</v>
+        <v>45016</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6858,11 +6858,16 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>6.5</v>
+        <v>19.8</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6889,20 +6894,52 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="W56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/artfynd/S 1135-2023 artfynd.xlsx", "S 1135-2023")</f>
+        <v/>
+      </c>
+      <c r="X56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/kartor/S 1135-2023 karta.png", "S 1135-2023")</f>
+        <v/>
+      </c>
+      <c r="Y56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/kartor_geotiff/S 1135-2023 georefererad karta.tif", "S 1135-2023")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/klagomål/S 1135-2023 FSC-klagomål.docx", "S 1135-2023")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/klagomålsmail/S 1135-2023 FSC-klagomål mail.docx", "S 1135-2023")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/tillsyn/S 1135-2023 tillsynsbegäran.docx", "S 1135-2023")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1860/tillsynsmail/S 1135-2023 tillsynsbegäran mail.docx", "S 1135-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36346-2022</t>
+          <t>A 5441-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6916,10 +6953,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44803</v>
+        <v>44595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,13 +6968,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6980,7 +7012,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36349-2022</t>
+          <t>A 36346-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6997,7 +7029,7 @@
         <v>44803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7047,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7058,7 +7090,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36351-2022</t>
+          <t>A 36349-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7075,7 +7107,7 @@
         <v>44803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7093,7 +7125,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7136,7 +7168,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9665-2022</t>
+          <t>A 36351-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7150,10 +7182,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44617</v>
+        <v>44803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7165,8 +7197,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7209,7 +7246,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28119-2022</t>
+          <t>A 9665-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7223,10 +7260,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44746</v>
+        <v>44617</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7238,13 +7275,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7287,7 +7319,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59907-2021</t>
+          <t>A 28119-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7301,10 +7333,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44494</v>
+        <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7316,8 +7348,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7360,7 +7397,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1104-2022</t>
+          <t>A 59907-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7374,10 +7411,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44571</v>
+        <v>44494</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7390,7 +7427,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7433,7 +7470,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40960-2022</t>
+          <t>A 1104-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7447,10 +7484,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44825</v>
+        <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7462,13 +7499,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7511,7 +7543,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38539-2022</t>
+          <t>A 40960-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7525,10 +7557,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44813</v>
+        <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7546,7 +7578,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7589,7 +7621,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10041-2022</t>
+          <t>A 38539-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7603,10 +7635,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44621</v>
+        <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7618,8 +7650,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7662,7 +7699,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15502-2022</t>
+          <t>A 10041-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7676,10 +7713,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44662</v>
+        <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7691,13 +7728,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7740,7 +7772,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36348-2022</t>
+          <t>A 15502-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7754,10 +7786,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44803</v>
+        <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7775,7 +7807,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7818,7 +7850,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37137-2022</t>
+          <t>A 36348-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7832,10 +7864,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44805</v>
+        <v>44803</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7847,8 +7879,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>12</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7891,7 +7928,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36520-2022</t>
+          <t>A 37137-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7905,10 +7942,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44804</v>
+        <v>44805</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7921,7 +7958,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7964,7 +8001,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8898-2022</t>
+          <t>A 36520-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7978,10 +8015,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44614</v>
+        <v>44804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7991,11 +8028,6 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>LAXÅ</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -8042,7 +8074,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 69035-2021</t>
+          <t>A 8898-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8056,10 +8088,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44530</v>
+        <v>44614</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8073,11 +8105,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8120,7 +8152,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2372-2022</t>
+          <t>A 69035-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8134,10 +8166,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44579</v>
+        <v>44530</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8149,8 +8181,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8193,7 +8230,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15518-2022</t>
+          <t>A 2372-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8207,10 +8244,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44662</v>
+        <v>44579</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8222,13 +8259,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8271,7 +8303,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 62423-2021</t>
+          <t>A 15518-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8285,10 +8317,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44503</v>
+        <v>44662</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8306,7 +8338,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8349,7 +8381,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 978-2022</t>
+          <t>A 62423-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8359,14 +8391,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44571</v>
+        <v>44503</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8384,7 +8416,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8427,7 +8459,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62437-2021</t>
+          <t>A 978-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8437,14 +8469,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44503</v>
+        <v>44571</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8462,7 +8494,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8505,7 +8537,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28566-2025</t>
+          <t>A 62437-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8519,10 +8551,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45819</v>
+        <v>44503</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8534,8 +8566,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8578,7 +8615,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6902-2025</t>
+          <t>A 28566-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8592,10 +8629,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45701</v>
+        <v>45819</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8607,13 +8644,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8656,7 +8688,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10673-2023</t>
+          <t>A 6902-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8670,10 +8702,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44988</v>
+        <v>45701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8691,7 +8723,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8734,7 +8766,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28415-2025</t>
+          <t>A 10673-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8748,10 +8780,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45819</v>
+        <v>44988</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8763,8 +8795,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8807,7 +8844,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12060-2024</t>
+          <t>A 28415-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8821,10 +8858,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45377</v>
+        <v>45819</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8836,13 +8873,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8885,7 +8917,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12065-2024</t>
+          <t>A 12060-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8902,7 +8934,7 @@
         <v>45377</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8920,7 +8952,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8963,7 +8995,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38547-2022</t>
+          <t>A 12065-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8977,10 +9009,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44813</v>
+        <v>45377</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8998,7 +9030,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9041,7 +9073,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38554-2022</t>
+          <t>A 38547-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9058,7 +9090,7 @@
         <v>44813</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9076,7 +9108,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9119,7 +9151,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61677-2022</t>
+          <t>A 38554-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9133,10 +9165,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44917</v>
+        <v>44813</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9148,8 +9180,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9192,7 +9229,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40815-2024</t>
+          <t>A 61677-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9206,10 +9243,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45558</v>
+        <v>44917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9221,13 +9258,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9270,7 +9302,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40668-2025</t>
+          <t>A 40815-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9284,10 +9316,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45896</v>
+        <v>45558</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9299,8 +9331,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9343,7 +9380,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19177-2023</t>
+          <t>A 40668-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9357,10 +9394,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45048</v>
+        <v>45896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9372,13 +9409,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9421,7 +9453,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34594-2022</t>
+          <t>A 19177-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9435,10 +9467,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44795</v>
+        <v>45048</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9450,8 +9482,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9494,7 +9531,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62594-2023</t>
+          <t>A 34594-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9508,10 +9545,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45271</v>
+        <v>44795</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9524,7 +9561,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9567,7 +9604,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23072-2026</t>
+          <t>A 62594-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9581,10 +9618,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46161</v>
+        <v>45271</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9596,13 +9633,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9645,7 +9677,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23074-2026</t>
+          <t>A 23072-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9662,7 +9694,7 @@
         <v>46161</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9680,7 +9712,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9723,7 +9755,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23076-2026</t>
+          <t>A 23074-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9740,7 +9772,7 @@
         <v>46161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9758,7 +9790,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9801,7 +9833,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54093-2023</t>
+          <t>A 23076-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9811,14 +9843,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45225</v>
+        <v>46161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9830,8 +9862,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9874,7 +9911,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5917-2023</t>
+          <t>A 54093-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9884,14 +9921,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44963</v>
+        <v>45225</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9904,7 +9941,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9947,7 +9984,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23068-2026</t>
+          <t>A 5917-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9961,10 +9998,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46161</v>
+        <v>44963</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9976,13 +10013,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10025,7 +10057,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23071-2026</t>
+          <t>A 23068-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10042,7 +10074,7 @@
         <v>46161</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10060,7 +10092,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10103,7 +10135,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23075-2026</t>
+          <t>A 23071-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10120,7 +10152,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10138,7 +10170,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10181,7 +10213,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23073-2026</t>
+          <t>A 23075-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10198,7 +10230,7 @@
         <v>46161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10259,7 +10291,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34535-2024</t>
+          <t>A 23073-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10273,10 +10305,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45525</v>
+        <v>46161</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10288,8 +10320,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10332,7 +10369,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44313-2025</t>
+          <t>A 34535-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10346,10 +10383,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45915</v>
+        <v>45525</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10362,7 +10399,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10405,7 +10442,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14008-2024</t>
+          <t>A 44313-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10415,14 +10452,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45392</v>
+        <v>45915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10434,13 +10471,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10483,7 +10515,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45424-2025</t>
+          <t>A 14008-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10493,14 +10525,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45920</v>
+        <v>45392</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10512,8 +10544,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10556,7 +10593,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28112-2022</t>
+          <t>A 45424-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10570,10 +10607,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44746</v>
+        <v>45920</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10585,13 +10622,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10634,7 +10666,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24741-2026</t>
+          <t>A 28112-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10648,10 +10680,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46171</v>
+        <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10669,7 +10701,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10712,7 +10744,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21005-2024</t>
+          <t>A 24741-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10726,10 +10758,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45439</v>
+        <v>46171</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10741,8 +10773,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10785,7 +10822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34218-2023</t>
+          <t>A 21005-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10799,10 +10836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45126</v>
+        <v>45439</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10815,7 +10852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10858,7 +10895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 34225-2023</t>
+          <t>A 34218-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10875,7 +10912,7 @@
         <v>45126</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10888,7 +10925,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10931,7 +10968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25602-2023</t>
+          <t>A 34225-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10945,10 +10982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45089</v>
+        <v>45126</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10960,13 +10997,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11009,7 +11041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38613-2023</t>
+          <t>A 25602-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11023,10 +11055,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45160</v>
+        <v>45089</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11038,8 +11070,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11082,7 +11119,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21522-2024</t>
+          <t>A 38613-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11092,14 +11129,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45441</v>
+        <v>45160</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11112,7 +11149,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11155,7 +11192,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57497-2023</t>
+          <t>A 21522-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11165,14 +11202,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45240</v>
+        <v>45441</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11185,7 +11222,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11228,7 +11265,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57503-2023</t>
+          <t>A 57497-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11245,7 +11282,7 @@
         <v>45240</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11258,7 +11295,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11.5</v>
+        <v>8.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11301,7 +11338,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53016-2023</t>
+          <t>A 57503-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11311,14 +11348,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45226</v>
+        <v>45240</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11330,13 +11367,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11379,7 +11411,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54511-2023</t>
+          <t>A 53016-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11389,14 +11421,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45233</v>
+        <v>45226</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11410,11 +11442,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11457,7 +11489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23674-2024</t>
+          <t>A 54511-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11471,10 +11503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45454</v>
+        <v>45233</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11486,8 +11518,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11530,7 +11567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25921-2026</t>
+          <t>A 23674-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11544,10 +11581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46178</v>
+        <v>45454</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11559,13 +11596,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11608,7 +11640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 33774-2022</t>
+          <t>A 25921-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11622,10 +11654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44790</v>
+        <v>46178</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11686,7 +11718,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51462-2025</t>
+          <t>A 33774-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11700,10 +11732,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45950</v>
+        <v>44790</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11721,7 +11753,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11764,7 +11796,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25926-2026</t>
+          <t>A 51462-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11778,10 +11810,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46178</v>
+        <v>45950</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11799,7 +11831,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11842,7 +11874,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8530-2025</t>
+          <t>A 25926-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11856,10 +11888,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45709</v>
+        <v>46178</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11877,7 +11909,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11920,7 +11952,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25920-2026</t>
+          <t>A 8530-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11934,10 +11966,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46178</v>
+        <v>45709</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11955,7 +11987,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11998,7 +12030,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25922-2026</t>
+          <t>A 25920-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12015,7 +12047,7 @@
         <v>46178</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12033,7 +12065,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12076,7 +12108,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33930-2023</t>
+          <t>A 25922-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12090,10 +12122,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45134</v>
+        <v>46178</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12105,8 +12137,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12149,7 +12186,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53092-2025</t>
+          <t>A 33930-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12163,10 +12200,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45958</v>
+        <v>45134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12179,7 +12216,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12222,7 +12259,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26883-2026</t>
+          <t>A 53092-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12236,10 +12273,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46185</v>
+        <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12251,13 +12288,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12300,7 +12332,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26877-2026</t>
+          <t>A 26883-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12317,7 +12349,7 @@
         <v>46185</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12335,7 +12367,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12378,7 +12410,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26878-2026</t>
+          <t>A 26877-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12395,7 +12427,7 @@
         <v>46185</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12413,7 +12445,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12456,7 +12488,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26880-2026</t>
+          <t>A 26878-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12473,7 +12505,7 @@
         <v>46185</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12491,7 +12523,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12534,7 +12566,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26879-2026</t>
+          <t>A 26880-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12551,7 +12583,7 @@
         <v>46185</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12569,7 +12601,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12612,7 +12644,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61091-2023</t>
+          <t>A 26879-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12626,10 +12658,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45261</v>
+        <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12647,7 +12679,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12690,7 +12722,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31189-2024</t>
+          <t>A 61091-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12704,10 +12736,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45503</v>
+        <v>45261</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12719,8 +12751,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12763,7 +12800,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31190-2024</t>
+          <t>A 31189-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12780,7 +12817,7 @@
         <v>45503</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12793,7 +12830,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12836,7 +12873,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21548-2024</t>
+          <t>A 31190-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12850,10 +12887,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45441</v>
+        <v>45503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12866,7 +12903,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12909,7 +12946,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55202-2025</t>
+          <t>A 21548-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12919,14 +12956,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45968</v>
+        <v>45441</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12938,13 +12975,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12987,7 +13019,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 54901-2025</t>
+          <t>A 55202-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12997,14 +13029,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13016,8 +13048,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13060,7 +13097,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 34567-2024</t>
+          <t>A 54901-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13074,10 +13111,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45525</v>
+        <v>45967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13090,7 +13127,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13133,7 +13170,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28821-2026</t>
+          <t>A 34567-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13147,10 +13184,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46198</v>
+        <v>45525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13163,7 +13200,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13206,7 +13243,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28827-2026</t>
+          <t>A 28821-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13223,7 +13260,7 @@
         <v>46198</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13236,7 +13273,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13279,7 +13316,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 48782-2024</t>
+          <t>A 28827-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13293,10 +13330,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45593</v>
+        <v>46198</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13308,13 +13345,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13357,7 +13389,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 56668-2025</t>
+          <t>A 48782-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13371,10 +13403,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45975</v>
+        <v>45593</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13386,8 +13418,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>18.1</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13430,7 +13467,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 57425-2025</t>
+          <t>A 56668-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13444,10 +13481,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45980</v>
+        <v>45975</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13460,7 +13497,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>18.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13503,7 +13540,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29161-2026</t>
+          <t>A 57425-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13517,10 +13554,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46202</v>
+        <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13532,13 +13569,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13581,7 +13613,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29163-2026</t>
+          <t>A 29161-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13598,7 +13630,7 @@
         <v>46202</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13616,7 +13648,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13659,7 +13691,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29176-2026</t>
+          <t>A 29163-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13676,7 +13708,7 @@
         <v>46202</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13694,7 +13726,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13737,7 +13769,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10496-2024</t>
+          <t>A 29176-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13751,10 +13783,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45366</v>
+        <v>46202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13772,7 +13804,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13815,7 +13847,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13104-2025</t>
+          <t>A 10496-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13829,10 +13861,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45734</v>
+        <v>45366</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13844,8 +13876,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13888,7 +13925,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60392-2023</t>
+          <t>A 13104-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13902,10 +13939,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45259</v>
+        <v>45734</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13917,13 +13954,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13966,7 +13998,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12651-2024</t>
+          <t>A 60392-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13980,10 +14012,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45384</v>
+        <v>45259</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14001,7 +14033,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -14044,7 +14076,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 58690-2025</t>
+          <t>A 12651-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -14058,10 +14090,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45986</v>
+        <v>45384</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14079,7 +14111,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14122,7 +14154,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6452-2024</t>
+          <t>A 58690-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14136,10 +14168,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45338</v>
+        <v>45986</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14151,8 +14183,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14195,7 +14232,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26412-2023</t>
+          <t>A 6452-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14209,10 +14246,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45092</v>
+        <v>45338</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14224,13 +14261,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14273,7 +14305,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59770-2025</t>
+          <t>A 26412-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14287,10 +14319,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45992</v>
+        <v>45092</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14308,7 +14340,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14351,7 +14383,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 41601-2023</t>
+          <t>A 59770-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14365,10 +14397,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45175</v>
+        <v>45992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14380,8 +14412,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14424,7 +14461,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 1662-2024</t>
+          <t>A 41601-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14438,10 +14475,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45306</v>
+        <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14454,7 +14491,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14497,7 +14534,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 30813-2026</t>
+          <t>A 1662-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14511,10 +14548,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46212</v>
+        <v>45306</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14526,13 +14563,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14575,7 +14607,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 60685-2025</t>
+          <t>A 30813-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14589,10 +14621,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45996</v>
+        <v>46212</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14610,7 +14642,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14653,7 +14685,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 50402-2023</t>
+          <t>A 60685-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14667,10 +14699,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45216</v>
+        <v>45996</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14682,8 +14714,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14726,7 +14763,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 21474-2025</t>
+          <t>A 50402-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14736,14 +14773,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45782</v>
+        <v>45216</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14755,13 +14792,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14804,7 +14836,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62029-2025</t>
+          <t>A 21474-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14814,14 +14846,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46003</v>
+        <v>45782</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14833,8 +14865,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14877,7 +14914,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 21212-2023</t>
+          <t>A 62029-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14891,10 +14928,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45062</v>
+        <v>46003</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14907,7 +14944,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14950,7 +14987,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32208-2026</t>
+          <t>A 21212-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14964,10 +15001,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46237</v>
+        <v>45062</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14980,7 +15017,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -15023,7 +15060,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37771-2026</t>
+          <t>A 32208-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -15033,14 +15070,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46279</v>
+        <v>46237</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15053,7 +15090,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -15096,7 +15133,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6299-2024</t>
+          <t>A 37771-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15106,14 +15143,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45338</v>
+        <v>46279</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15169,7 +15206,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23234-2025</t>
+          <t>A 6299-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15183,10 +15220,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45791</v>
+        <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15198,13 +15235,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15247,7 +15279,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 598-2026</t>
+          <t>A 23234-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15261,10 +15293,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46029</v>
+        <v>45791</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15282,7 +15314,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15325,7 +15357,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1772-2026</t>
+          <t>A 598-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15339,10 +15371,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15356,11 +15388,11 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15403,7 +15435,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 2332-2026</t>
+          <t>A 1772-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15417,10 +15449,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15434,11 +15466,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15481,7 +15513,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1944-2026</t>
+          <t>A 2332-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15495,10 +15527,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15516,7 +15548,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15559,7 +15591,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1943-2026</t>
+          <t>A 1944-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15576,7 +15608,7 @@
         <v>46035</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15594,7 +15626,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>10.9</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15637,7 +15669,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2102-2026</t>
+          <t>A 1943-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15651,10 +15683,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15672,7 +15704,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>10.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15715,7 +15747,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2127-2026</t>
+          <t>A 2102-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15732,7 +15764,7 @@
         <v>46036</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15750,7 +15782,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15793,7 +15825,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18845-2023</t>
+          <t>A 2127-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15807,10 +15839,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45042</v>
+        <v>46036</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15822,8 +15854,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15866,7 +15903,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 5414-2026</t>
+          <t>A 18845-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15880,10 +15917,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46048</v>
+        <v>45042</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15896,7 +15933,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15939,7 +15976,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 4417-2026</t>
+          <t>A 5414-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15953,10 +15990,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15969,7 +16006,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -16012,7 +16049,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 5421-2026</t>
+          <t>A 4417-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16026,10 +16063,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46048</v>
+        <v>46045</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16042,7 +16079,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -16085,7 +16122,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 5650-2026</t>
+          <t>A 5421-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -16095,14 +16132,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46051</v>
+        <v>46048</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16112,11 +16149,6 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>LAXÅ</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -16163,7 +16195,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 517-2026</t>
+          <t>A 5650-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16173,14 +16205,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46029</v>
+        <v>46051</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16194,11 +16226,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16241,7 +16273,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56555-2024</t>
+          <t>A 517-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16255,10 +16287,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45625</v>
+        <v>46029</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16270,8 +16302,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16314,7 +16351,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9107-2026</t>
+          <t>A 56555-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16328,10 +16365,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46069</v>
+        <v>45625</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16343,13 +16380,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16392,7 +16424,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 9108-2026</t>
+          <t>A 9107-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16409,7 +16441,7 @@
         <v>46069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16427,7 +16459,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16470,7 +16502,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 9110-2026</t>
+          <t>A 9108-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16487,7 +16519,7 @@
         <v>46069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16505,7 +16537,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16548,7 +16580,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 9112-2026</t>
+          <t>A 9110-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16565,7 +16597,7 @@
         <v>46069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16583,7 +16615,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16626,7 +16658,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 29087-2025</t>
+          <t>A 9112-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16640,10 +16672,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45821</v>
+        <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16661,7 +16693,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16704,7 +16736,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 29089-2025</t>
+          <t>A 29087-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16721,7 +16753,7 @@
         <v>45821</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16739,7 +16771,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16782,7 +16814,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29090-2025</t>
+          <t>A 29089-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16792,14 +16824,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16817,7 +16849,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16860,7 +16892,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 9987-2026</t>
+          <t>A 29090-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16870,14 +16902,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46073</v>
+        <v>45821</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16895,7 +16927,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16938,7 +16970,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 9986-2026</t>
+          <t>A 9987-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16955,7 +16987,7 @@
         <v>46073</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16973,7 +17005,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -17016,7 +17048,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30334-2025</t>
+          <t>A 9986-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -17030,10 +17062,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45827</v>
+        <v>46073</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17051,7 +17083,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -17094,7 +17126,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30384-2025</t>
+          <t>A 30334-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -17111,7 +17143,7 @@
         <v>45827</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17129,7 +17161,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17172,7 +17204,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11653-2026</t>
+          <t>A 30384-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17186,10 +17218,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46084</v>
+        <v>45827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17207,7 +17239,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17250,7 +17282,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 33282-2025</t>
+          <t>A 11653-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17264,10 +17296,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45840</v>
+        <v>46084</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17281,11 +17313,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17328,7 +17360,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 14876-2026</t>
+          <t>A 33282-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17342,10 +17374,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46104</v>
+        <v>45840</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17359,11 +17391,11 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17406,7 +17438,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 15341-2026</t>
+          <t>A 14876-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17420,10 +17452,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17441,7 +17473,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17484,7 +17516,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 14877-2026</t>
+          <t>A 15341-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17498,10 +17530,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17519,7 +17551,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17562,7 +17594,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 15317-2026</t>
+          <t>A 14877-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17576,10 +17608,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17597,7 +17629,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17640,7 +17672,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 15314-2026</t>
+          <t>A 15317-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17657,7 +17689,7 @@
         <v>46105</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17718,7 +17750,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 15433-2026</t>
+          <t>A 15314-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17732,10 +17764,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17753,7 +17785,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>12.4</v>
+        <v>1.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17796,7 +17828,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 41402-2026</t>
+          <t>A 15433-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17810,10 +17842,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46300</v>
+        <v>46106</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17825,8 +17857,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>3.3</v>
+        <v>12.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17869,7 +17906,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 16483-2026</t>
+          <t>A 41402-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17883,10 +17920,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46112</v>
+        <v>46300</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17896,11 +17933,6 @@
       <c r="G201" t="inlineStr">
         <is>
           <t>LAXÅ</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -17947,7 +17979,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 36672-2025</t>
+          <t>A 16483-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17961,10 +17993,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45873</v>
+        <v>46112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17982,7 +18014,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -18025,7 +18057,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36670-2025</t>
+          <t>A 36672-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -18042,7 +18074,7 @@
         <v>45873</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18060,7 +18092,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -18103,7 +18135,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37620-2025</t>
+          <t>A 36670-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -18117,10 +18149,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45880</v>
+        <v>45873</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18132,8 +18164,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -18176,7 +18213,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12962-2025</t>
+          <t>A 37620-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18190,10 +18227,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45734</v>
+        <v>45880</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18205,13 +18242,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18254,7 +18286,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 6905-2025</t>
+          <t>A 12962-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18268,10 +18300,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45701</v>
+        <v>45734</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18289,7 +18321,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18332,7 +18364,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 51714-2022</t>
+          <t>A 6905-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18346,10 +18378,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44872</v>
+        <v>45701</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18367,7 +18399,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18410,7 +18442,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 40151-2024</t>
+          <t>A 51714-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18424,10 +18456,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45554</v>
+        <v>44872</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18445,7 +18477,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18488,7 +18520,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36553-2024</t>
+          <t>A 40151-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18502,10 +18534,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45537</v>
+        <v>45554</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18523,7 +18555,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18566,7 +18598,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 68356-2021</t>
+          <t>A 36553-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18580,10 +18612,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44528</v>
+        <v>45537</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18601,7 +18633,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>9.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18644,7 +18676,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 67054-2021</t>
+          <t>A 68356-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18658,10 +18690,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44522</v>
+        <v>44528</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18673,8 +18705,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18717,7 +18754,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 13888-2024</t>
+          <t>A 67054-2021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18731,10 +18768,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45391</v>
+        <v>44522</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18747,7 +18784,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18790,7 +18827,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 22381-2025</t>
+          <t>A 13888-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18804,10 +18841,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45786</v>
+        <v>45391</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18819,13 +18856,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18868,7 +18900,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 12430-2023</t>
+          <t>A 22381-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18882,10 +18914,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44998</v>
+        <v>45786</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18897,8 +18929,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18941,7 +18978,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35850-2024</t>
+          <t>A 12430-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18955,10 +18992,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45532</v>
+        <v>44998</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18971,7 +19008,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -19014,7 +19051,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 28396-2025</t>
+          <t>A 35850-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -19028,10 +19065,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45819</v>
+        <v>45532</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19044,7 +19081,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -19087,7 +19124,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 6294-2024</t>
+          <t>A 28396-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19101,10 +19138,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45338</v>
+        <v>45819</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19117,7 +19154,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -19160,7 +19197,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 55484-2024</t>
+          <t>A 6294-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -19174,10 +19211,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45622</v>
+        <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19189,13 +19226,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19238,7 +19270,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33695-2023</t>
+          <t>A 55484-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19252,10 +19284,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45132</v>
+        <v>45622</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19267,8 +19299,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19311,7 +19348,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 20943-2026</t>
+          <t>A 33695-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19325,10 +19362,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46142</v>
+        <v>45132</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19340,13 +19377,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19389,7 +19421,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 12063-2024</t>
+          <t>A 20943-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19403,10 +19435,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45377</v>
+        <v>46142</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19424,7 +19456,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19467,7 +19499,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21764-2022</t>
+          <t>A 12063-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19481,10 +19513,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44708</v>
+        <v>45377</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19496,8 +19528,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19540,7 +19577,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 48849-2023</t>
+          <t>A 21764-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19554,10 +19591,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45209</v>
+        <v>44708</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19570,7 +19607,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19613,7 +19650,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 542-2026</t>
+          <t>A 48849-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19627,10 +19664,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46029</v>
+        <v>45209</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19642,13 +19679,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19691,7 +19723,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22501-2026</t>
+          <t>A 542-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19705,10 +19737,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46155</v>
+        <v>46029</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19722,11 +19754,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19769,7 +19801,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 6158-2025</t>
+          <t>A 22501-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19783,10 +19815,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45698</v>
+        <v>46155</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19804,7 +19836,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19847,7 +19879,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 50578-2024</t>
+          <t>A 6158-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19861,10 +19893,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45601</v>
+        <v>45698</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19876,8 +19908,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19920,7 +19957,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 22493-2026</t>
+          <t>A 50578-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19934,10 +19971,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46155</v>
+        <v>45601</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19949,13 +19986,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19998,7 +20030,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 41456-2023</t>
+          <t>A 22493-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -20012,10 +20044,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45175</v>
+        <v>46155</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20027,8 +20059,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -20071,7 +20108,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 25512-2023</t>
+          <t>A 41456-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -20085,10 +20122,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45089</v>
+        <v>45175</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20100,13 +20137,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -20149,7 +20181,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 25515-2023</t>
+          <t>A 25512-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -20166,7 +20198,7 @@
         <v>45089</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20184,7 +20216,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20227,7 +20259,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 10680-2023</t>
+          <t>A 25515-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20241,10 +20273,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44988</v>
+        <v>45089</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20258,11 +20290,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20305,7 +20337,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 67053-2021</t>
+          <t>A 10680-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20319,10 +20351,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44522</v>
+        <v>44988</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20334,8 +20366,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20378,7 +20415,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 57548-2023</t>
+          <t>A 67053-2021</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20392,10 +20429,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45240</v>
+        <v>44522</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20408,7 +20445,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20451,7 +20488,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 16682-2024</t>
+          <t>A 57548-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20465,10 +20502,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45408</v>
+        <v>45240</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20480,13 +20517,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20529,7 +20561,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 33692-2023</t>
+          <t>A 16682-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20543,10 +20575,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45132</v>
+        <v>45408</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20558,8 +20590,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20602,7 +20639,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 33696-2023</t>
+          <t>A 33692-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20619,7 +20656,7 @@
         <v>45132</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20632,7 +20669,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20675,7 +20712,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 57521-2023</t>
+          <t>A 33696-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20689,10 +20726,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45240</v>
+        <v>45132</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20705,7 +20742,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20748,7 +20785,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 57534-2023</t>
+          <t>A 57521-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20765,7 +20802,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20778,7 +20815,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20821,7 +20858,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 15650-2023</t>
+          <t>A 57534-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20835,10 +20872,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45021</v>
+        <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20851,7 +20888,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20894,7 +20931,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 11139-2023</t>
+          <t>A 15650-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20908,10 +20945,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44987</v>
+        <v>45021</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20924,7 +20961,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20967,7 +21004,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 54411-2022</t>
+          <t>A 11139-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20981,10 +21018,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44879</v>
+        <v>44987</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20997,7 +21034,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -21040,7 +21077,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 33186-2023</t>
+          <t>A 54411-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -21054,10 +21091,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45127</v>
+        <v>44879</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21070,7 +21107,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -21113,7 +21150,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 15380-2025</t>
+          <t>A 33186-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -21127,10 +21164,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45747</v>
+        <v>45127</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21143,7 +21180,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -21186,7 +21223,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 13102-2025</t>
+          <t>A 15380-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -21200,10 +21237,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45734</v>
+        <v>45747</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21216,7 +21253,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21259,7 +21296,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 57515-2023</t>
+          <t>A 13102-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21273,10 +21310,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45240</v>
+        <v>45734</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21289,7 +21326,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21332,7 +21369,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 19816-2025</t>
+          <t>A 57515-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21346,10 +21383,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45771</v>
+        <v>45240</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21361,13 +21398,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I247" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21410,7 +21442,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 19820-2025</t>
+          <t>A 19816-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21427,7 +21459,7 @@
         <v>45771</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21445,7 +21477,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21488,7 +21520,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 58052-2023</t>
+          <t>A 19820-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -21502,10 +21534,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45245</v>
+        <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21517,8 +21549,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -21561,7 +21598,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 62405-2021</t>
+          <t>A 58052-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -21575,10 +21612,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44503</v>
+        <v>45245</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21590,13 +21627,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -21639,7 +21671,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 60748-2023</t>
+          <t>A 62405-2021</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -21653,10 +21685,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45260</v>
+        <v>44503</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21674,7 +21706,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -21717,7 +21749,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 25744-2023</t>
+          <t>A 60748-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21731,10 +21763,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45090</v>
+        <v>45260</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21752,7 +21784,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21795,7 +21827,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 57747-2022</t>
+          <t>A 25744-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21809,10 +21841,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44897</v>
+        <v>45090</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21830,7 +21862,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21873,7 +21905,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 56135-2022</t>
+          <t>A 57747-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -21887,10 +21919,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44886</v>
+        <v>44897</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21900,6 +21932,11 @@
       <c r="G254" t="inlineStr">
         <is>
           <t>LAXÅ</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I254" t="n">
@@ -21946,7 +21983,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 15213-2024</t>
+          <t>A 56135-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21960,10 +21997,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45400</v>
+        <v>44886</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21975,13 +22012,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -22024,7 +22056,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 14205-2025</t>
+          <t>A 15213-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -22034,14 +22066,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45740</v>
+        <v>45400</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22059,7 +22091,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -22102,7 +22134,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 6305-2024</t>
+          <t>A 14205-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -22112,14 +22144,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45338</v>
+        <v>45740</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22129,6 +22161,11 @@
       <c r="G257" t="inlineStr">
         <is>
           <t>LAXÅ</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I257" t="n">
@@ -22175,7 +22212,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 36420-2024</t>
+          <t>A 6305-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -22189,10 +22226,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45536</v>
+        <v>45338</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22205,7 +22242,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -22248,7 +22285,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 50265-2024</t>
+          <t>A 36420-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -22262,10 +22299,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45600</v>
+        <v>45536</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22278,7 +22315,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -22321,7 +22358,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 38620-2023</t>
+          <t>A 50265-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -22335,10 +22372,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45160</v>
+        <v>45600</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22351,7 +22388,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -22394,7 +22431,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 7132-2024</t>
+          <t>A 38620-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -22408,10 +22445,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45344</v>
+        <v>45160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22424,7 +22461,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -22467,7 +22504,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 61051-2023</t>
+          <t>A 7132-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -22481,10 +22518,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45261</v>
+        <v>45344</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22496,13 +22533,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I262" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -22545,7 +22577,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 9312-2024</t>
+          <t>A 61051-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -22559,10 +22591,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45358</v>
+        <v>45261</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22574,8 +22606,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I263" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -22618,7 +22655,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 6178-2024</t>
+          <t>A 9312-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -22632,10 +22669,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45337</v>
+        <v>45358</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22647,13 +22684,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I264" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -22696,7 +22728,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 33929-2023</t>
+          <t>A 6178-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -22710,10 +22742,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45134</v>
+        <v>45337</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22725,8 +22757,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I265" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -22769,7 +22806,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 38288-2023</t>
+          <t>A 33929-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -22783,10 +22820,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45161</v>
+        <v>45134</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22799,7 +22836,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -22842,7 +22879,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 11476-2023</t>
+          <t>A 38288-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -22856,10 +22893,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44993</v>
+        <v>45161</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22871,13 +22908,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I267" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -22920,7 +22952,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 62454-2021</t>
+          <t>A 11476-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -22934,10 +22966,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44503</v>
+        <v>44993</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22955,7 +22987,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -22998,7 +23030,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 11477-2023</t>
+          <t>A 62454-2021</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -23012,10 +23044,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44993</v>
+        <v>44503</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23033,7 +23065,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -23076,7 +23108,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 67052-2021</t>
+          <t>A 11477-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -23090,10 +23122,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44522</v>
+        <v>44993</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23105,8 +23137,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I270" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -23149,7 +23186,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 7932-2024</t>
+          <t>A 67052-2021</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -23163,10 +23200,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45349</v>
+        <v>44522</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23179,7 +23216,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -23222,7 +23259,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 41853-2024</t>
+          <t>A 7932-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -23236,10 +23273,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45561</v>
+        <v>45349</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23252,7 +23289,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -23295,7 +23332,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 50262-2024</t>
+          <t>A 41853-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -23309,10 +23346,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45600</v>
+        <v>45561</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23325,7 +23362,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -23368,7 +23405,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 49881-2024</t>
+          <t>A 50262-2024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -23382,10 +23419,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45597</v>
+        <v>45600</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23397,13 +23434,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I274" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -23446,7 +23478,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 25563-2022</t>
+          <t>A 49881-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -23460,10 +23492,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>44732</v>
+        <v>45597</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23475,8 +23507,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I275" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -23519,7 +23556,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 19809-2025</t>
+          <t>A 25563-2022</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -23533,10 +23570,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45771</v>
+        <v>44732</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23548,13 +23585,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I276" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -23597,7 +23629,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 19813-2025</t>
+          <t>A 19809-2025</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -23614,7 +23646,7 @@
         <v>45771</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23632,7 +23664,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -23675,7 +23707,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 19835-2025</t>
+          <t>A 19813-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -23685,14 +23717,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D278" s="1" t="n">
         <v>45771</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23710,7 +23742,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -23753,7 +23785,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 37570-2023</t>
+          <t>A 19835-2025</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -23763,14 +23795,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45159</v>
+        <v>45771</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23788,7 +23820,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -23831,7 +23863,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 34437-2022</t>
+          <t>A 37570-2023</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -23845,10 +23877,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>44792</v>
+        <v>45159</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23860,8 +23892,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I280" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -23904,7 +23941,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 14462-2025</t>
+          <t>A 34437-2022</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -23918,10 +23955,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45741</v>
+        <v>44792</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23933,13 +23970,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I281" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -23982,7 +24014,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 54640-2023</t>
+          <t>A 14462-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -23996,10 +24028,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45234</v>
+        <v>45741</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24011,8 +24043,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I282" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -24055,7 +24092,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 15130-2025</t>
+          <t>A 54640-2023</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -24065,14 +24102,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45744</v>
+        <v>45234</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24084,13 +24121,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I283" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -24133,7 +24165,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 35130-2022</t>
+          <t>A 15130-2025</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -24143,14 +24175,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>44797</v>
+        <v>45744</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24162,8 +24194,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I284" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -24206,7 +24243,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 19807-2025</t>
+          <t>A 35130-2022</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -24216,14 +24253,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>45771</v>
+        <v>44797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24235,13 +24272,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I285" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -24284,7 +24316,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 6300-2024</t>
+          <t>A 19807-2025</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -24298,10 +24330,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45338</v>
+        <v>45771</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24313,8 +24345,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I286" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -24357,7 +24394,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 60732-2023</t>
+          <t>A 6300-2024</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -24371,10 +24408,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>45260</v>
+        <v>45338</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24386,13 +24423,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I287" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -24435,7 +24467,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 22927-2024</t>
+          <t>A 60732-2023</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -24449,10 +24481,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45448</v>
+        <v>45260</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24464,8 +24496,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I288" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -24508,7 +24545,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 52442-2022</t>
+          <t>A 22927-2024</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -24522,10 +24559,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>44874</v>
+        <v>45448</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24537,13 +24574,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I289" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -24586,7 +24618,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 34481-2022</t>
+          <t>A 52442-2022</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -24600,10 +24632,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>44792</v>
+        <v>44874</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24613,6 +24645,11 @@
       <c r="G290" t="inlineStr">
         <is>
           <t>LAXÅ</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I290" t="n">
@@ -24659,7 +24696,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 7137-2024</t>
+          <t>A 34481-2022</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -24673,10 +24710,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45344</v>
+        <v>44792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24689,7 +24726,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -24732,7 +24769,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 34585-2022</t>
+          <t>A 7137-2024</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -24746,10 +24783,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>44795</v>
+        <v>45344</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24762,7 +24799,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -24805,7 +24842,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 51822-2022</t>
+          <t>A 34585-2022</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -24819,10 +24856,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>44872</v>
+        <v>44795</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24834,13 +24871,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I293" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -24883,7 +24915,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 36567-2024</t>
+          <t>A 51822-2022</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -24897,10 +24929,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45537</v>
+        <v>44872</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24918,7 +24950,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -24961,7 +24993,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 36544-2024</t>
+          <t>A 36567-2024</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -24978,7 +25010,7 @@
         <v>45537</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24996,7 +25028,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -25039,7 +25071,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 15641-2024</t>
+          <t>A 36544-2024</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -25053,10 +25085,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>45403</v>
+        <v>45537</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25068,8 +25100,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I296" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -25112,7 +25149,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 7130-2024</t>
+          <t>A 15641-2024</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -25126,10 +25163,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>45344</v>
+        <v>45403</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25142,7 +25179,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -25185,7 +25222,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A 36421-2024</t>
+          <t>A 7130-2024</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -25199,10 +25236,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>45536</v>
+        <v>45344</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25215,7 +25252,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -25258,7 +25295,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 62439-2021</t>
+          <t>A 36421-2024</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -25272,10 +25309,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>44503</v>
+        <v>45536</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25287,13 +25324,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I299" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -25336,7 +25368,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A 6842-2022</t>
+          <t>A 62439-2021</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -25350,10 +25382,10 @@
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>44602</v>
+        <v>44503</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25365,8 +25397,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I300" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -25409,7 +25446,7 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
-          <t>A 59455-2022</t>
+          <t>A 6842-2022</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -25423,10 +25460,10 @@
         </is>
       </c>
       <c r="D301" s="1" t="n">
-        <v>44907</v>
+        <v>44602</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25438,13 +25475,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I301" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
@@ -25487,7 +25519,7 @@
     <row r="302" ht="15" customHeight="1">
       <c r="A302" t="inlineStr">
         <is>
-          <t>A 3443-2023</t>
+          <t>A 59455-2022</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -25501,10 +25533,10 @@
         </is>
       </c>
       <c r="D302" s="1" t="n">
-        <v>44949</v>
+        <v>44907</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25516,8 +25548,13 @@
           <t>LAXÅ</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -25560,7 +25597,7 @@
     <row r="303" ht="15" customHeight="1">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A 44076-2024</t>
+          <t>A 3443-2023</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -25574,10 +25611,10 @@
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>45572</v>
+        <v>44949</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25590,7 +25627,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -25633,7 +25670,7 @@
     <row r="304" ht="15" customHeight="1">
       <c r="A304" t="inlineStr">
         <is>
-          <t>A 59892-2021</t>
+          <t>A 44076-2024</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -25647,10 +25684,10 @@
         </is>
       </c>
       <c r="D304" s="1" t="n">
-        <v>44494</v>
+        <v>45572</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25663,7 +25700,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J304" t="n">
         <v>0</v>
@@ -25706,24 +25743,24 @@
     <row r="305" ht="15" customHeight="1">
       <c r="A305" t="inlineStr">
         <is>
-          <t>S 705-2024</t>
+          <t>A 59892-2021</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D305" s="1" t="n">
-        <v>45362</v>
+        <v>44494</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25735,13 +25772,8 @@
           <t>LAXÅ</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I305" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -25784,7 +25816,7 @@
     <row r="306" ht="15" customHeight="1">
       <c r="A306" t="inlineStr">
         <is>
-          <t>S 1135-2023</t>
+          <t>S 705-2024</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -25798,10 +25830,10 @@
         </is>
       </c>
       <c r="D306" s="1" t="n">
-        <v>45016</v>
+        <v>45362</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25819,7 +25851,7 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>19.8</v>
+        <v>2</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -25879,7 +25911,7 @@
         <v>44889</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25957,7 +25989,7 @@
         <v>45007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26035,7 +26067,7 @@
         <v>45362</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26113,7 +26145,7 @@
         <v>45117</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26191,7 +26223,7 @@
         <v>44903</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26269,7 +26301,7 @@
         <v>45007</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26347,7 +26379,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26425,7 +26457,7 @@
         <v>45740</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26503,7 +26535,7 @@
         <v>45744</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26581,7 +26613,7 @@
         <v>45744</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26659,7 +26691,7 @@
         <v>45767</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26732,7 +26764,7 @@
         <v>45771</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26810,7 +26842,7 @@
         <v>45782</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26888,7 +26920,7 @@
         <v>45821</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26966,7 +26998,7 @@
         <v>45968</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27044,7 +27076,7 @@
         <v>46262</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
